--- a/1. ELICITACION/1.3 Historias de Usuario/GN°4_Matriz de Marco de Trabajo HU_V2.xlsx
+++ b/1. ELICITACION/1.3 Historias de Usuario/GN°4_Matriz de Marco de Trabajo HU_V2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoshPC\Documents\Universidad\Analisis y Diseño\Unidad2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoshPC\Documents\Universidad\Analisis y Diseño\Github\YulianaValencia_30724_G4_ADSW\1. ELICITACION\1.3 Historias de Usuario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66846A47-3BC7-4D33-A057-C8EDEDAE4572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F816D0-865B-4915-A459-86335E405EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1147,14 +1147,22 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1164,26 +1172,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1195,6 +1183,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9418,7 +9418,7 @@
       <c r="F5" s="17"/>
     </row>
     <row r="6" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="67" t="s">
         <v>172</v>
       </c>
       <c r="C6" s="41"/>
@@ -9488,12 +9488,12 @@
         <v>1</v>
       </c>
       <c r="D9" s="27"/>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="53" t="s">
         <v>173</v>
       </c>
       <c r="F9" s="42"/>
       <c r="G9" s="27"/>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="53" t="s">
         <v>11</v>
       </c>
       <c r="I9" s="42"/>
@@ -9512,13 +9512,13 @@
         <v>121</v>
       </c>
       <c r="D10" s="31"/>
-      <c r="E10" s="45" t="str">
+      <c r="E10" s="68" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,5,0)</f>
         <v>Administrador</v>
       </c>
       <c r="F10" s="42"/>
       <c r="G10" s="32"/>
-      <c r="H10" s="46" t="str">
+      <c r="H10" s="54" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,11,0)</f>
         <v>Por hacer</v>
       </c>
@@ -9539,12 +9539,12 @@
         <v>174</v>
       </c>
       <c r="D11" s="31"/>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="53" t="s">
         <v>10</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="32"/>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="53" t="s">
         <v>175</v>
       </c>
       <c r="I11" s="42"/>
@@ -9574,13 +9574,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="31"/>
-      <c r="E12" s="46" t="str">
+      <c r="E12" s="54" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,10,0)</f>
         <v>Alta</v>
       </c>
       <c r="F12" s="42"/>
       <c r="G12" s="32"/>
-      <c r="H12" s="46" t="str">
+      <c r="H12" s="54" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,7,0)</f>
         <v>Yuliana Valencia</v>
       </c>
@@ -9634,34 +9634,34 @@
     <row r="14" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18"/>
       <c r="B14" s="25"/>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="55" t="s">
         <v>176</v>
       </c>
-      <c r="D14" s="61" t="str">
+      <c r="D14" s="49" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,3,0)</f>
         <v>Consultar los técnicos registrados.</v>
       </c>
-      <c r="E14" s="51"/>
+      <c r="E14" s="44"/>
       <c r="F14" s="34"/>
-      <c r="G14" s="47" t="s">
+      <c r="G14" s="55" t="s">
         <v>177</v>
       </c>
-      <c r="H14" s="61" t="str">
+      <c r="H14" s="49" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,4,0)</f>
         <v>Encontrar técnicos mediante búsquedas, filtros y ordenaciones.</v>
       </c>
-      <c r="I14" s="58"/>
-      <c r="J14" s="51"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="44"/>
       <c r="K14" s="34"/>
-      <c r="L14" s="47" t="s">
+      <c r="L14" s="55" t="s">
         <v>178</v>
       </c>
-      <c r="M14" s="62" t="str">
+      <c r="M14" s="58" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,6,0)</f>
         <v>Diseñar tabla interactiva para el módulo de técnicos.</v>
       </c>
-      <c r="N14" s="58"/>
-      <c r="O14" s="51"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="44"/>
       <c r="P14" s="29"/>
       <c r="Q14" s="18"/>
       <c r="R14" s="18"/>
@@ -9677,19 +9677,19 @@
     <row r="15" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="25"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="46"/>
       <c r="F15" s="34"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="59"/>
-      <c r="J15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="46"/>
       <c r="K15" s="34"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="59"/>
-      <c r="O15" s="56"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="45"/>
+      <c r="N15" s="51"/>
+      <c r="O15" s="46"/>
       <c r="P15" s="29"/>
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
@@ -9705,19 +9705,19 @@
     <row r="16" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="25"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="53"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="48"/>
       <c r="F16" s="34"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="53"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="48"/>
       <c r="K16" s="34"/>
-      <c r="L16" s="49"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="60"/>
-      <c r="O16" s="53"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="47"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="48"/>
       <c r="P16" s="29"/>
       <c r="Q16" s="18"/>
       <c r="R16" s="18"/>
@@ -9760,42 +9760,42 @@
     </row>
     <row r="18" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="25"/>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="65" t="s">
         <v>179</v>
       </c>
-      <c r="D18" s="51"/>
-      <c r="E18" s="63" t="str">
+      <c r="D18" s="44"/>
+      <c r="E18" s="59" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,14,0)</f>
         <v>Consultar Técnicos</v>
       </c>
-      <c r="F18" s="64"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="64"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="64"/>
-      <c r="O18" s="65"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="61"/>
       <c r="P18" s="29"/>
       <c r="Q18" s="18"/>
     </row>
     <row r="19" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="25"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="67"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="67"/>
-      <c r="K19" s="67"/>
-      <c r="L19" s="67"/>
-      <c r="M19" s="67"/>
-      <c r="N19" s="67"/>
-      <c r="O19" s="68"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="64"/>
       <c r="P19" s="29"/>
       <c r="Q19" s="18"/>
     </row>
@@ -9820,29 +9820,29 @@
     <row r="21" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>
       <c r="B21" s="25"/>
-      <c r="C21" s="54" t="s">
+      <c r="C21" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="57" t="str">
+      <c r="D21" s="44"/>
+      <c r="E21" s="66" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,12,0)</f>
         <v>Buscar un técnico por nombre y verificar que la tabla se filtre.</v>
       </c>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="51"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="44"/>
       <c r="I21" s="28"/>
-      <c r="J21" s="54" t="s">
+      <c r="J21" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="K21" s="51"/>
-      <c r="L21" s="61">
+      <c r="K21" s="44"/>
+      <c r="L21" s="49">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,13,0)</f>
         <v>0</v>
       </c>
-      <c r="M21" s="58"/>
-      <c r="N21" s="58"/>
-      <c r="O21" s="51"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="44"/>
       <c r="P21" s="29"/>
       <c r="Q21" s="18"/>
       <c r="R21" s="18"/>
@@ -9858,19 +9858,19 @@
     <row r="22" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18"/>
       <c r="B22" s="25"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="56"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="46"/>
       <c r="I22" s="28"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="56"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="59"/>
-      <c r="O22" s="56"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="45"/>
+      <c r="M22" s="51"/>
+      <c r="N22" s="51"/>
+      <c r="O22" s="46"/>
       <c r="P22" s="29"/>
       <c r="Q22" s="18"/>
       <c r="R22" s="18"/>
@@ -9886,19 +9886,19 @@
     <row r="23" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18"/>
       <c r="B23" s="25"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="53"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="48"/>
       <c r="I23" s="28"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="52"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="60"/>
-      <c r="O23" s="53"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="52"/>
+      <c r="O23" s="48"/>
       <c r="P23" s="29"/>
       <c r="Q23" s="18"/>
       <c r="R23" s="18"/>
@@ -11299,6 +11299,15 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="C21:D23"/>
+    <mergeCell ref="E21:H23"/>
+    <mergeCell ref="B6:P6"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="H10:I10"/>
     <mergeCell ref="J21:K23"/>
     <mergeCell ref="L21:O23"/>
     <mergeCell ref="H11:I11"/>
@@ -11311,15 +11320,6 @@
     <mergeCell ref="E18:O19"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="C21:D23"/>
-    <mergeCell ref="E21:H23"/>
-    <mergeCell ref="B6:P6"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="H10:I10"/>
   </mergeCells>
   <conditionalFormatting sqref="H10:I10">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">

--- a/1. ELICITACION/1.3 Historias de Usuario/GN°4_Matriz de Marco de Trabajo HU_V2.xlsx
+++ b/1. ELICITACION/1.3 Historias de Usuario/GN°4_Matriz de Marco de Trabajo HU_V2.xlsx
@@ -1147,31 +1147,43 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1183,18 +1195,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9418,7 +9418,7 @@
       <c r="F5" s="17"/>
     </row>
     <row r="6" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="57" t="s">
         <v>172</v>
       </c>
       <c r="C6" s="41"/>
@@ -9488,12 +9488,12 @@
         <v>1</v>
       </c>
       <c r="D9" s="27"/>
-      <c r="E9" s="53" t="s">
+      <c r="E9" s="58" t="s">
         <v>173</v>
       </c>
       <c r="F9" s="42"/>
       <c r="G9" s="27"/>
-      <c r="H9" s="53" t="s">
+      <c r="H9" s="58" t="s">
         <v>11</v>
       </c>
       <c r="I9" s="42"/>
@@ -9512,13 +9512,13 @@
         <v>121</v>
       </c>
       <c r="D10" s="31"/>
-      <c r="E10" s="68" t="str">
+      <c r="E10" s="59" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,5,0)</f>
         <v>Administrador</v>
       </c>
       <c r="F10" s="42"/>
       <c r="G10" s="32"/>
-      <c r="H10" s="54" t="str">
+      <c r="H10" s="60" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,11,0)</f>
         <v>Por hacer</v>
       </c>
@@ -9539,12 +9539,12 @@
         <v>174</v>
       </c>
       <c r="D11" s="31"/>
-      <c r="E11" s="53" t="s">
+      <c r="E11" s="58" t="s">
         <v>10</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="32"/>
-      <c r="H11" s="53" t="s">
+      <c r="H11" s="58" t="s">
         <v>175</v>
       </c>
       <c r="I11" s="42"/>
@@ -9574,13 +9574,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="31"/>
-      <c r="E12" s="54" t="str">
+      <c r="E12" s="60" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,10,0)</f>
         <v>Alta</v>
       </c>
       <c r="F12" s="42"/>
       <c r="G12" s="32"/>
-      <c r="H12" s="54" t="str">
+      <c r="H12" s="60" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,7,0)</f>
         <v>Yuliana Valencia</v>
       </c>
@@ -9634,34 +9634,34 @@
     <row r="14" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18"/>
       <c r="B14" s="25"/>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="D14" s="49" t="str">
+      <c r="D14" s="61" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,3,0)</f>
         <v>Consultar los técnicos registrados.</v>
       </c>
-      <c r="E14" s="44"/>
+      <c r="E14" s="47"/>
       <c r="F14" s="34"/>
-      <c r="G14" s="55" t="s">
+      <c r="G14" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="H14" s="49" t="str">
+      <c r="H14" s="61" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,4,0)</f>
         <v>Encontrar técnicos mediante búsquedas, filtros y ordenaciones.</v>
       </c>
-      <c r="I14" s="50"/>
-      <c r="J14" s="44"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="47"/>
       <c r="K14" s="34"/>
-      <c r="L14" s="55" t="s">
+      <c r="L14" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="M14" s="58" t="str">
+      <c r="M14" s="62" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,6,0)</f>
         <v>Diseñar tabla interactiva para el módulo de técnicos.</v>
       </c>
-      <c r="N14" s="50"/>
-      <c r="O14" s="44"/>
+      <c r="N14" s="54"/>
+      <c r="O14" s="47"/>
       <c r="P14" s="29"/>
       <c r="Q14" s="18"/>
       <c r="R14" s="18"/>
@@ -9677,19 +9677,19 @@
     <row r="15" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="25"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="46"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="52"/>
       <c r="F15" s="34"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="46"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="52"/>
       <c r="K15" s="34"/>
-      <c r="L15" s="56"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="51"/>
-      <c r="O15" s="46"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="51"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="52"/>
       <c r="P15" s="29"/>
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
@@ -9705,19 +9705,19 @@
     <row r="16" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="25"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="48"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="49"/>
       <c r="F16" s="34"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="48"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="49"/>
       <c r="K16" s="34"/>
-      <c r="L16" s="57"/>
-      <c r="M16" s="47"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="48"/>
+      <c r="L16" s="45"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="49"/>
       <c r="P16" s="29"/>
       <c r="Q16" s="18"/>
       <c r="R16" s="18"/>
@@ -9760,42 +9760,42 @@
     </row>
     <row r="18" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="25"/>
-      <c r="C18" s="65" t="s">
+      <c r="C18" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="59" t="str">
+      <c r="D18" s="47"/>
+      <c r="E18" s="63" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,14,0)</f>
         <v>Consultar Técnicos</v>
       </c>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="60"/>
-      <c r="L18" s="60"/>
-      <c r="M18" s="60"/>
-      <c r="N18" s="60"/>
-      <c r="O18" s="61"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="65"/>
       <c r="P18" s="29"/>
       <c r="Q18" s="18"/>
     </row>
     <row r="19" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="25"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="63"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="63"/>
-      <c r="N19" s="63"/>
-      <c r="O19" s="64"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="67"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="67"/>
+      <c r="K19" s="67"/>
+      <c r="L19" s="67"/>
+      <c r="M19" s="67"/>
+      <c r="N19" s="67"/>
+      <c r="O19" s="68"/>
       <c r="P19" s="29"/>
       <c r="Q19" s="18"/>
     </row>
@@ -9820,29 +9820,29 @@
     <row r="21" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>
       <c r="B21" s="25"/>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="50" t="s">
         <v>180</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="66" t="str">
+      <c r="D21" s="47"/>
+      <c r="E21" s="53" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,12,0)</f>
         <v>Buscar un técnico por nombre y verificar que la tabla se filtre.</v>
       </c>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="44"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="47"/>
       <c r="I21" s="28"/>
-      <c r="J21" s="43" t="s">
+      <c r="J21" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="K21" s="44"/>
-      <c r="L21" s="49">
+      <c r="K21" s="47"/>
+      <c r="L21" s="61">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,13,0)</f>
         <v>0</v>
       </c>
-      <c r="M21" s="50"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="44"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="47"/>
       <c r="P21" s="29"/>
       <c r="Q21" s="18"/>
       <c r="R21" s="18"/>
@@ -9858,19 +9858,19 @@
     <row r="22" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18"/>
       <c r="B22" s="25"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="46"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="52"/>
       <c r="I22" s="28"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="45"/>
-      <c r="M22" s="51"/>
-      <c r="N22" s="51"/>
-      <c r="O22" s="46"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="52"/>
       <c r="P22" s="29"/>
       <c r="Q22" s="18"/>
       <c r="R22" s="18"/>
@@ -9886,19 +9886,19 @@
     <row r="23" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18"/>
       <c r="B23" s="25"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="49"/>
       <c r="I23" s="28"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="52"/>
-      <c r="N23" s="52"/>
-      <c r="O23" s="48"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="49"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="56"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="49"/>
       <c r="P23" s="29"/>
       <c r="Q23" s="18"/>
       <c r="R23" s="18"/>
@@ -11299,6 +11299,11 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="M14:O16"/>
+    <mergeCell ref="E18:O19"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="C18:D19"/>
     <mergeCell ref="C21:D23"/>
@@ -11315,11 +11320,6 @@
     <mergeCell ref="D14:E16"/>
     <mergeCell ref="G14:G16"/>
     <mergeCell ref="H14:J16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="M14:O16"/>
-    <mergeCell ref="E18:O19"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
   </mergeCells>
   <conditionalFormatting sqref="H10:I10">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">

--- a/1. ELICITACION/1.3 Historias de Usuario/GN°4_Matriz de Marco de Trabajo HU_V2.xlsx
+++ b/1. ELICITACION/1.3 Historias de Usuario/GN°4_Matriz de Marco de Trabajo HU_V2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoshPC\Documents\Universidad\Analisis y Diseño\Github\YulianaValencia_30724_G4_ADSW\1. ELICITACION\1.3 Historias de Usuario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F816D0-865B-4915-A459-86335E405EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0001282-B66E-4520-BACE-2E8927741C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1152,41 +1152,17 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1195,6 +1171,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9418,7 +9418,7 @@
       <c r="F5" s="17"/>
     </row>
     <row r="6" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="66" t="s">
         <v>172</v>
       </c>
       <c r="C6" s="41"/>
@@ -9488,12 +9488,12 @@
         <v>1</v>
       </c>
       <c r="D9" s="27"/>
-      <c r="E9" s="58" t="s">
+      <c r="E9" s="61" t="s">
         <v>173</v>
       </c>
       <c r="F9" s="42"/>
       <c r="G9" s="27"/>
-      <c r="H9" s="58" t="s">
+      <c r="H9" s="61" t="s">
         <v>11</v>
       </c>
       <c r="I9" s="42"/>
@@ -9512,13 +9512,13 @@
         <v>121</v>
       </c>
       <c r="D10" s="31"/>
-      <c r="E10" s="59" t="str">
+      <c r="E10" s="67" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,5,0)</f>
         <v>Administrador</v>
       </c>
       <c r="F10" s="42"/>
       <c r="G10" s="32"/>
-      <c r="H10" s="60" t="str">
+      <c r="H10" s="62" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,11,0)</f>
         <v>Por hacer</v>
       </c>
@@ -9539,12 +9539,12 @@
         <v>174</v>
       </c>
       <c r="D11" s="31"/>
-      <c r="E11" s="58" t="s">
+      <c r="E11" s="61" t="s">
         <v>10</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="32"/>
-      <c r="H11" s="58" t="s">
+      <c r="H11" s="61" t="s">
         <v>175</v>
       </c>
       <c r="I11" s="42"/>
@@ -9574,13 +9574,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="31"/>
-      <c r="E12" s="60" t="str">
+      <c r="E12" s="62" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,10,0)</f>
         <v>Alta</v>
       </c>
       <c r="F12" s="42"/>
       <c r="G12" s="32"/>
-      <c r="H12" s="60" t="str">
+      <c r="H12" s="62" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,7,0)</f>
         <v>Yuliana Valencia</v>
       </c>
@@ -9637,31 +9637,31 @@
       <c r="C14" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="D14" s="61" t="str">
+      <c r="D14" s="68" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,3,0)</f>
         <v>Consultar los técnicos registrados.</v>
       </c>
-      <c r="E14" s="47"/>
+      <c r="E14" s="48"/>
       <c r="F14" s="34"/>
       <c r="G14" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="H14" s="61" t="str">
+      <c r="H14" s="68" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,4,0)</f>
         <v>Encontrar técnicos mediante búsquedas, filtros y ordenaciones.</v>
       </c>
-      <c r="I14" s="54"/>
-      <c r="J14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="48"/>
       <c r="K14" s="34"/>
       <c r="L14" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="M14" s="62" t="str">
+      <c r="M14" s="46" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,6,0)</f>
         <v>Diseñar tabla interactiva para el módulo de técnicos.</v>
       </c>
-      <c r="N14" s="54"/>
-      <c r="O14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="48"/>
       <c r="P14" s="29"/>
       <c r="Q14" s="18"/>
       <c r="R14" s="18"/>
@@ -9678,18 +9678,18 @@
       <c r="A15" s="18"/>
       <c r="B15" s="25"/>
       <c r="C15" s="44"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="52"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="51"/>
       <c r="F15" s="34"/>
       <c r="G15" s="44"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="52"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="51"/>
       <c r="K15" s="34"/>
       <c r="L15" s="44"/>
-      <c r="M15" s="51"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="52"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="51"/>
       <c r="P15" s="29"/>
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
@@ -9706,18 +9706,18 @@
       <c r="A16" s="18"/>
       <c r="B16" s="25"/>
       <c r="C16" s="45"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="49"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="54"/>
       <c r="F16" s="34"/>
       <c r="G16" s="45"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="49"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="54"/>
       <c r="K16" s="34"/>
       <c r="L16" s="45"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="49"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="54"/>
       <c r="P16" s="29"/>
       <c r="Q16" s="18"/>
       <c r="R16" s="18"/>
@@ -9760,42 +9760,42 @@
     </row>
     <row r="18" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="25"/>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="63" t="s">
         <v>179</v>
       </c>
-      <c r="D18" s="47"/>
-      <c r="E18" s="63" t="str">
+      <c r="D18" s="48"/>
+      <c r="E18" s="55" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,14,0)</f>
         <v>Consultar Técnicos</v>
       </c>
-      <c r="F18" s="64"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="64"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="64"/>
-      <c r="O18" s="65"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="56"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="57"/>
       <c r="P18" s="29"/>
       <c r="Q18" s="18"/>
     </row>
     <row r="19" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="25"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="67"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="67"/>
-      <c r="K19" s="67"/>
-      <c r="L19" s="67"/>
-      <c r="M19" s="67"/>
-      <c r="N19" s="67"/>
-      <c r="O19" s="68"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="59"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="59"/>
+      <c r="O19" s="60"/>
       <c r="P19" s="29"/>
       <c r="Q19" s="18"/>
     </row>
@@ -9820,29 +9820,29 @@
     <row r="21" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>
       <c r="B21" s="25"/>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="64" t="s">
         <v>180</v>
       </c>
-      <c r="D21" s="47"/>
-      <c r="E21" s="53" t="str">
+      <c r="D21" s="48"/>
+      <c r="E21" s="65" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,12,0)</f>
         <v>Buscar un técnico por nombre y verificar que la tabla se filtre.</v>
       </c>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="48"/>
       <c r="I21" s="28"/>
-      <c r="J21" s="50" t="s">
+      <c r="J21" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="K21" s="47"/>
-      <c r="L21" s="61">
+      <c r="K21" s="48"/>
+      <c r="L21" s="68">
         <f>VLOOKUP(C10,'Formato descripción HU'!$B$5:$O$23,13,0)</f>
         <v>0</v>
       </c>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="47"/>
+      <c r="M21" s="47"/>
+      <c r="N21" s="47"/>
+      <c r="O21" s="48"/>
       <c r="P21" s="29"/>
       <c r="Q21" s="18"/>
       <c r="R21" s="18"/>
@@ -9858,19 +9858,19 @@
     <row r="22" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18"/>
       <c r="B22" s="25"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="52"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="51"/>
       <c r="I22" s="28"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="52"/>
-      <c r="L22" s="51"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="52"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="49"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="51"/>
       <c r="P22" s="29"/>
       <c r="Q22" s="18"/>
       <c r="R22" s="18"/>
@@ -9886,19 +9886,19 @@
     <row r="23" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18"/>
       <c r="B23" s="25"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="49"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="54"/>
       <c r="I23" s="28"/>
-      <c r="J23" s="48"/>
-      <c r="K23" s="49"/>
-      <c r="L23" s="48"/>
-      <c r="M23" s="56"/>
-      <c r="N23" s="56"/>
-      <c r="O23" s="49"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="54"/>
       <c r="P23" s="29"/>
       <c r="Q23" s="18"/>
       <c r="R23" s="18"/>
@@ -11299,11 +11299,6 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="M14:O16"/>
-    <mergeCell ref="E18:O19"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="C18:D19"/>
     <mergeCell ref="C21:D23"/>
@@ -11320,6 +11315,11 @@
     <mergeCell ref="D14:E16"/>
     <mergeCell ref="G14:G16"/>
     <mergeCell ref="H14:J16"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="M14:O16"/>
+    <mergeCell ref="E18:O19"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
   </mergeCells>
   <conditionalFormatting sqref="H10:I10">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
